--- a/KatalonData/EmailTextToPay/BillFileLookUp_SearchButton_Prod.xlsx
+++ b/KatalonData/EmailTextToPay/BillFileLookUp_SearchButton_Prod.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="25">
   <si>
     <t>Result</t>
   </si>
@@ -105,6 +105,12 @@
   </si>
   <si>
     <t>Tue Mar 24 19:39:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 23 15:58:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 23 15:58:57 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -577,7 +583,7 @@
         <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>9</v>
@@ -593,7 +599,7 @@
         <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>10</v>

--- a/KatalonData/EmailTextToPay/BillFileLookUp_SearchButton_Prod.xlsx
+++ b/KatalonData/EmailTextToPay/BillFileLookUp_SearchButton_Prod.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="28">
   <si>
     <t>Result</t>
   </si>
@@ -111,6 +111,15 @@
   </si>
   <si>
     <t>Thu Apr 23 15:58:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 11:09:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 11:09:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 11:10:27 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -526,7 +535,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F033DD18-DD0F-43E3-A2D0-6223D1731E2C}">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="6.36328125" collapsed="true"/>
@@ -579,11 +588,11 @@
       </c>
     </row>
     <row customFormat="1" ht="13" r="2" s="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>19</v>
       </c>
-      <c r="B2" t="s">
-        <v>23</v>
+      <c r="B2" t="s" s="0">
+        <v>25</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>9</v>
@@ -595,11 +604,11 @@
       <c r="L2" s="3"/>
     </row>
     <row customFormat="1" ht="13" r="3" s="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>19</v>
       </c>
-      <c r="B3" t="s">
-        <v>24</v>
+      <c r="B3" t="s" s="0">
+        <v>26</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>10</v>
@@ -613,11 +622,11 @@
       <c r="L3" s="3"/>
     </row>
     <row customFormat="1" ht="13" r="4" s="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="0">
         <v>19</v>
       </c>
-      <c r="B4" t="s">
-        <v>22</v>
+      <c r="B4" t="s" s="0">
+        <v>27</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>11</v>
